--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_magallanes_y_la_antartica_chilena.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>36.87580025608194</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>24.33234421364987</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>-7.120743034055732</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>16.88888888888889</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>14.54545454545453</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>12.55813953488372</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>32.05128205128205</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>136.6666666666667</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>7.03125</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -602,9 +570,6 @@
       </c>
       <c r="E11">
         <v>-45.63106796116504</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
